--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42524-2025 artfynd.xlsx
+++ b/artfynd/A 42524-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128802016</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
